--- a/DateBase/orders/Nha Thu_2026-5-27.xlsx
+++ b/DateBase/orders/Nha Thu_2026-5-27.xlsx
@@ -784,6 +784,9 @@
         <v xml:space="preserve">497_小飞燕粉色_delphinium ballkleid
 pink_undefined_1bunch</v>
       </c>
+      <c r="F41" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -842,7 +845,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>03331454510101555101020050101055533335551551015153530351550</v>
+        <v>03331454510101555101020050101055533335551551015153530351555</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-5-27.xlsx
+++ b/DateBase/orders/Nha Thu_2026-5-27.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L82"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -788,9 +788,356 @@
         <v>5</v>
       </c>
     </row>
+    <row r="42">
+      <c r="C42" t="str">
+        <v>360_夕雾草_undefined_Trachelium caeruleum L._1bunch</v>
+      </c>
+      <c r="F42" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="str">
+        <v>548_白星花_tweedia white_undefined_1bunch</v>
+      </c>
+      <c r="F43" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="str">
+        <v>354_桔叶_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F44" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="str">
+        <v>344_钢草_steal grass_Xanthorrhoea preissii Endl._1bunch</v>
+      </c>
+      <c r="F45" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="46" xml:space="preserve">
+      <c r="A46" t="str">
+        <v>3</v>
+      </c>
+      <c r="C46" t="str" xml:space="preserve">
+        <v xml:space="preserve">448_吊米 绿_hanging amaranthus
+green_undefined_1bunch</v>
+      </c>
+      <c r="F46" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" t="str">
+        <v>478_绿芯向日葵_sunflower mini_undefined_1bunch</v>
+      </c>
+      <c r="F47" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" t="str">
+        <v>383_油画向日葵_sunflower black_undefined_1bunch</v>
+      </c>
+      <c r="F48" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="C49" t="str">
+        <v>384_奶油向日葵_sunflower cream_undefined_1bunch</v>
+      </c>
+      <c r="F49" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="C50" t="str">
+        <v>154_莫泊_Moab_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F50" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="str">
+        <v>144_高原红_High Plateau Red_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F51" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="C52" t="str">
+        <v>189_洛神_Mandala_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F52" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="C53" t="str">
+        <v>604_康乃馨粉佳人_pink_undefined_20stems</v>
+      </c>
+      <c r="F53" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>4</v>
+      </c>
+      <c r="C54" t="str">
+        <v>189_洛神_Mandala_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F54" t="str">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="C55" t="str">
+        <v>147_娜欧米_Red Naomi_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F55" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="C56" t="str">
+        <v>175_火灵鸟_Free Spirit_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F56" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="C57" t="str">
+        <v>192_粉荔枝_Pink Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F57" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="C58" t="str">
+        <v>623_多丁粉太子_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F58" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="C59" t="str">
+        <v>626_多丁莫言_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F59" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>5</v>
+      </c>
+      <c r="C60" t="str">
+        <v>192_粉荔枝_Pink Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F60" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" t="str">
+        <v>277_草莓杏仁饼_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F61" t="str">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="C62" t="str">
+        <v>274_仙子之吻_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F62" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="C63" t="str">
+        <v>221_朱丽叶塔_Julieta_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F63" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="C64" t="str">
+        <v>279_完美甜蜜_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F64" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="C65" t="str">
+        <v>625_多丁紫蝴蝶_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F65" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="C66" t="str">
+        <v>614_康乃馨绿_green_undefined_20stems</v>
+      </c>
+      <c r="F66" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="C67" t="str">
+        <v>612_康乃馨古巴爱情_cuba love_undefined_20stems</v>
+      </c>
+      <c r="F67" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="C68" t="str">
+        <v>606_康乃馨橙光_orange_undefined_20stems</v>
+      </c>
+      <c r="F68" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="C69" t="str">
+        <v>600_康乃馨复古红_vintage red_undefined_20stems</v>
+      </c>
+      <c r="F69" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>6</v>
+      </c>
+      <c r="C70" t="str">
+        <v>647_海棠果红_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F70" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="C71" t="str">
+        <v>524_海棠果绿_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F71" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="C72" t="str">
+        <v>107_绣球浅粉_Hydrangea Light Pink S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F72" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="C73" t="str">
+        <v>106_绣球粉_Hydrangea Pink S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F73" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="C74" t="str">
+        <v>100_绣球白_Hydrangea White S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F74" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="C75" t="str">
+        <v>602_康乃馨白_white_undefined_20stems</v>
+      </c>
+      <c r="F75" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="C76" t="str">
+        <v>615_康乃馨野马_horse_undefined_20stems</v>
+      </c>
+      <c r="F76" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>7</v>
+      </c>
+      <c r="C77" t="str">
+        <v>148_坦尼克_Tineke_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F77" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="C78" t="str">
+        <v>731_芍药冰点_undefined_undefined_10stems</v>
+      </c>
+      <c r="F78" t="str">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="C79" t="str">
+        <v>646_芍药莎拉_Sarah_undefined_5stems</v>
+      </c>
+      <c r="F79" t="str">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>8</v>
+      </c>
+      <c r="C80" t="str">
+        <v>762_芍药杨妃_undefined_undefined_10stems</v>
+      </c>
+      <c r="F80" t="str">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="C81" t="str">
+        <v>517_鼠尾粉色_veronica pink_undefined_1bunch</v>
+      </c>
+      <c r="F81" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="C82" t="str">
+        <v>790_铁线莲粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F82" t="str">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L82"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -845,7 +1192,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>03331454510101555101020050101055533335551551015153530351555</v>
+        <v>03331454510101555101020050101055533335551551015153530351555101053065551012510915851010109461010555101010303020105510010018055</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-5-27.xlsx
+++ b/DateBase/orders/Nha Thu_2026-5-27.xlsx
@@ -1194,6 +1194,9 @@
       <c r="G2" t="str">
         <v>03331454510101555101020050101055533335551551015153530351555101053065551012510915851010109461010555101010303020105510010018055</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
